--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_CMG HIDRÁULICA NB TORRENT.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_CMG HIDRÁULICA NB TORRENT.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA38"/>
+  <dimension ref="A1:BA42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>162.04</v>
+        <v>393.48</v>
       </c>
       <c r="C2" t="n">
-        <v>159.98</v>
+        <v>390.36</v>
       </c>
       <c r="D2" t="n">
-        <v>91.88648581072633</v>
+        <v>90.17317348088943</v>
       </c>
       <c r="E2" t="n">
-        <v>81.26015751968995</v>
+        <v>94.52812788195511</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3978102189781022</v>
+        <v>0.3986301369863013</v>
       </c>
       <c r="G2" t="n">
-        <v>0.157328461226147</v>
+        <v>0.1473960039305601</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3645833333333333</v>
+        <v>0.3740157480314961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2773722627737226</v>
+        <v>0.1671232876712329</v>
       </c>
       <c r="J2" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="O2" t="n">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4379562043795621</v>
+        <v>0.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08029197080291971</v>
+        <v>0.1041095890410959</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0364963503649635</v>
+        <v>0.0684931506849315</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="X2" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1751824817518248</v>
+        <v>0.1232876712328767</v>
       </c>
       <c r="Z2" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2700729927007299</v>
+        <v>0.3041095890410959</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.4863013698630137</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.25</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2432432432432433</v>
+        <v>0.2342342342342342</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.7377049180327869</v>
+        <v>0.75</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6764705882352942</v>
+        <v>0.5949367088607594</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.4421052631578947</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.363636363636364</v>
+        <v>1.793103448275862</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.8709677419354839</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.419354838709677</v>
+        <v>5.069444444444445</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.290322580645161</v>
+        <v>6.111111111111111</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.02</v>
+        <v>78.696</v>
       </c>
       <c r="C3" t="n">
-        <v>79.99000000000001</v>
+        <v>78.072</v>
       </c>
       <c r="D3" t="n">
-        <v>91.88648581072633</v>
+        <v>90.17317348088945</v>
       </c>
       <c r="E3" t="n">
-        <v>81.26015751968995</v>
+        <v>94.52812788195511</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3978102189781022</v>
+        <v>0.3986301369863013</v>
       </c>
       <c r="G3" t="n">
-        <v>0.157328461226147</v>
+        <v>0.1473960039305601</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3645833333333333</v>
+        <v>0.3740157480314961</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2773722627737226</v>
+        <v>0.1671232876712329</v>
       </c>
       <c r="J3" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>10.4</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="N3" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
+        <v>29.2</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4379562043795621</v>
+        <v>0.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="R3" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08029197080291971</v>
+        <v>0.1041095890410959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0364963503649635</v>
+        <v>0.0684931506849315</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1751824817518248</v>
+        <v>0.1232876712328767</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.5</v>
+        <v>22.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2700729927007299</v>
+        <v>0.3041095890410959</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.4863013698630137</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.2432432432432433</v>
+        <v>0.2342342342342343</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.7377049180327869</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6764705882352942</v>
+        <v>0.5949367088607594</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.4421052631578948</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.363636363636364</v>
+        <v>1.793103448275862</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8709677419354839</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.419354838709677</v>
+        <v>5.069444444444445</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.290322580645161</v>
+        <v>6.111111111111111</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>157.92</v>
+        <v>387.24</v>
       </c>
       <c r="C4" t="n">
-        <v>159.98</v>
+        <v>390.36</v>
       </c>
       <c r="D4" t="n">
-        <v>81.26015751968995</v>
+        <v>94.52812788195511</v>
       </c>
       <c r="E4" t="n">
-        <v>91.88648581072633</v>
+        <v>90.17317348088943</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3785714285714286</v>
+        <v>0.4386503067484663</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1762388554841385</v>
+        <v>0.1723987430167598</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3398058252427185</v>
+        <v>0.3271889400921659</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1714285714285714</v>
+        <v>0.254601226993865</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="K4" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="M4" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="N4" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="O4" t="n">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4785714285714286</v>
+        <v>0.4447852760736196</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.05521472392638037</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04285714285714286</v>
+        <v>0.04294478527607362</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1357142857142857</v>
+        <v>0.1226993865030675</v>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3071428571428572</v>
+        <v>0.3343558282208589</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4477611940298508</v>
+        <v>0.4758620689655172</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.186046511627907</v>
+        <v>0.2660550458715596</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.8955223880597015</v>
+        <v>0.9517241379310345</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.6290322580645161</v>
+        <v>0.825503355704698</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.7361111111111112</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.5070422535211268</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.625</v>
+        <v>1.894736842105263</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.117647058823529</v>
+        <v>4.126582278481012</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.852941176470588</v>
+        <v>5.075949367088608</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.96000000000001</v>
+        <v>77.44800000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>79.99000000000001</v>
+        <v>78.072</v>
       </c>
       <c r="D5" t="n">
-        <v>81.26015751968995</v>
+        <v>94.52812788195511</v>
       </c>
       <c r="E5" t="n">
-        <v>91.88648581072633</v>
+        <v>90.17317348088945</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3785714285714286</v>
+        <v>0.4386503067484663</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1762388554841385</v>
+        <v>0.1723987430167598</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3398058252427185</v>
+        <v>0.3271889400921659</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1714285714285714</v>
+        <v>0.2546012269938651</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="L5" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="O5" t="n">
-        <v>33.5</v>
+        <v>29</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4785714285714286</v>
+        <v>0.4447852760736196</v>
       </c>
       <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.05521472392638037</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.04294478527607361</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.1226993865030675</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.3343558282208589</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.4758620689655172</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="AE5" t="n">
         <v>0.5</v>
       </c>
-      <c r="R5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.03571428571428571</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.04285714285714286</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.1357142857142857</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.3071428571428572</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.4477611940298508</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.3333333333333333</v>
-      </c>
       <c r="AF5" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.186046511627907</v>
+        <v>0.2660550458715596</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.8955223880597015</v>
+        <v>0.9517241379310345</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.6290322580645161</v>
+        <v>0.8255033557046979</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.736111111111111</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.5070422535211268</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.625</v>
+        <v>1.894736842105263</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.117647058823529</v>
+        <v>4.126582278481012</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.852941176470588</v>
+        <v>5.075949367088607</v>
       </c>
     </row>
     <row r="7">
@@ -1429,22 +1429,22 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1483,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>01:09</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.353</v>
+        <v>0.136</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -1594,89 +1594,89 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>42</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I9" t="n">
+        <v>21</v>
+      </c>
+      <c r="J9" t="n">
+        <v>17</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14</v>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>24</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" t="n">
+      <c r="R9" t="n">
+        <v>17</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>14</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>9</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>16</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I9" t="n">
-        <v>12</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="Z9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
         <v>3</v>
       </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>12</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>6</v>
-      </c>
-      <c r="X9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -1693,63 +1693,63 @@
         <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AK9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL9" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.333</v>
+        <v>0.182</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>57:31</t>
+          <t>152:50</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>30.28</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.381</v>
+        <v>0.286</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.457</v>
+        <v>0.361</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.793</v>
+        <v>0.654</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.132</v>
+        <v>0.093</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.381</v>
+        <v>0.286</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.75</v>
+        <v>2.833</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.25</v>
+        <v>8.167</v>
       </c>
       <c r="AW9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.214</v>
+        <v>0.172</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.095</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.171</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="10">
@@ -1905,13 +1905,13 @@
         <v>3</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.26</v>
+        <v>0.262</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.109</v>
+        <v>0.103</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.102</v>
+        <v>0.121</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -1924,61 +1924,61 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
         <v>8</v>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3</v>
-      </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
@@ -1987,99 +1987,99 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
+        <v>5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AD11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI11" t="n">
         <v>2</v>
       </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AJ11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK11" t="n">
         <v>2</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1</v>
-      </c>
       <c r="AL11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>29:48</t>
+          <t>86:16</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>12.76</v>
+        <v>29.64</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.278</v>
+        <v>0.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.372</v>
+        <v>0.304</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.627</v>
+        <v>0.506</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.157</v>
+        <v>0.169</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.333</v>
+        <v>0.182</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.174</v>
+        <v>0.141</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.104</v>
+        <v>0.075</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="12">
@@ -2089,37 +2089,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>26</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M12" t="n">
         <v>2</v>
@@ -2131,67 +2131,67 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="U12" t="n">
         <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
         <v>0.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2204,47 +2204,47 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>42:08</t>
+          <t>118:59</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>21.08</v>
+        <v>49.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.333</v>
+        <v>0.409</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.332</v>
+        <v>0.391</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.474</v>
+        <v>0.625</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.285</v>
+        <v>0.202</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.167</v>
+        <v>0.121</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.203</v>
+        <v>0.171</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.099</v>
+        <v>0.079</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.184</v>
+        <v>0.178</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="13">
@@ -2254,22 +2254,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
@@ -2278,56 +2278,56 @@
         <v>3</v>
       </c>
       <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>11</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="n">
+      <c r="Z13" t="n">
         <v>3</v>
       </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>14</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2</v>
-      </c>
       <c r="AA13" t="n">
         <v>1</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -2362,54 +2362,54 @@
         <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.375</v>
+        <v>0.2</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>35:26</t>
+          <t>55:01</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>14.32</v>
+        <v>26.32</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.65</v>
+        <v>0.395</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.707</v>
+        <v>0.443</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.117</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.209</v>
+        <v>0.228</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.3</v>
+        <v>0.158</v>
       </c>
       <c r="AU13" t="n">
         <v>1</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.333</v>
+        <v>3.167</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.333</v>
+        <v>4.167</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.164</v>
+        <v>0.196</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.024</v>
+        <v>0.014</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.066</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="14">
@@ -2419,61 +2419,61 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>37</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" t="n">
+        <v>38</v>
+      </c>
+      <c r="F14" t="n">
         <v>2</v>
       </c>
-      <c r="C14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>13</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="E14" t="n">
-        <v>12</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="R14" t="n">
         <v>6</v>
       </c>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3</v>
-      </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2482,99 +2482,99 @@
         <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
         <v>0.375</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
         <v>3</v>
       </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>31:55</t>
+          <t>86:36</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>21.76</v>
+        <v>61.72</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.167</v>
+        <v>0.327</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.202</v>
+        <v>0.338</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.368</v>
+        <v>0.599</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.092</v>
+        <v>0.113</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.111</v>
+        <v>0.102</v>
       </c>
       <c r="AU14" t="n">
         <v>1</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.277</v>
+        <v>0.292</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.078</v>
+        <v>0.045</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.17</v>
+        <v>0.117</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.045</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="15">
@@ -2584,82 +2584,82 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
+        <v>17</v>
+      </c>
+      <c r="E15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>6</v>
       </c>
-      <c r="E15" t="n">
+      <c r="I15" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>18</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
         <v>11</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>11</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="U15" t="n">
         <v>2</v>
       </c>
       <c r="V15" t="n">
+        <v>9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>8</v>
+      </c>
+      <c r="X15" t="n">
         <v>4</v>
       </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
       <c r="Y15" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2699,47 +2699,47 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41:06</t>
+          <t>117:30</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>14.2</v>
+        <v>42.96</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.545</v>
+        <v>0.607</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.53</v>
+        <v>0.626</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.986</v>
+        <v>0.931</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.256</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.182</v>
+        <v>0.214</v>
       </c>
       <c r="AU15" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="AW15" t="n">
         <v>3</v>
       </c>
-      <c r="AV15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>14</v>
-      </c>
       <c r="AX15" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.223</v>
+        <v>0.168</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.076</v>
+        <v>0.141</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.073</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="16">
@@ -2749,187 +2749,187 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>39</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>24</v>
+      </c>
+      <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="C16" t="n">
-        <v>19</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>12</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" t="n">
+      <c r="M16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
         <v>4</v>
       </c>
-      <c r="G16" t="n">
-        <v>9</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V16" t="n">
         <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AK16" t="n">
         <v>3</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AL16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>92:12</t>
+        </is>
+      </c>
+      <c r="AO16" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="AU16" t="n">
         <v>3</v>
       </c>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>46:26</t>
-        </is>
-      </c>
-      <c r="AO16" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.316</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5</v>
-      </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>8.75</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>11.75</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.126</v>
+        <v>0.183</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.018</v>
+        <v>0.034</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.067</v>
+        <v>0.05</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>#55 L. BLASCO NAVARRO</t>
+          <t>#26 M. ISIDRO PEÑA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2938,16 +2938,16 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2956,25 +2956,25 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -2986,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2995,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -3019,33 +3019,33 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>24:18</t>
+          <t>02:08</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
@@ -3054,230 +3054,230 @@
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.134</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.137</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.224</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>#87 A. TERRADES DAROQUI</t>
+          <t>#33 Ó. GONZÁLEZ JURADO</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="C18" t="n">
-        <v>32</v>
-      </c>
-      <c r="D18" t="n">
-        <v>8</v>
-      </c>
-      <c r="E18" t="n">
-        <v>19</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>13</v>
-      </c>
-      <c r="I18" t="n">
-        <v>22</v>
-      </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4</v>
-      </c>
       <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="R18" t="n">
-        <v>5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>18</v>
-      </c>
       <c r="U18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="AO18" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AW18" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>54:05</t>
-        </is>
-      </c>
-      <c r="AO18" t="n">
-        <v>38.68</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7.25</v>
-      </c>
       <c r="AX18" t="n">
-        <v>0.29</v>
+        <v>0.292</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.062</v>
+        <v>0.145</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.144</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>#95 D. CALERO BAUTISTA</t>
+          <t>#55 L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3286,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -3298,28 +3298,28 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="U19" t="n">
         <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.75</v>
+        <v>0.455</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3331,567 +3331,567 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL19" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>28:31</t>
+          <t>90:27</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>13.64</v>
+        <v>32.76</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.387</v>
+        <v>0.469</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.66</v>
+        <v>0.824</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.147</v>
+        <v>0.122</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.333</v>
+        <v>0.111</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.5</v>
+        <v>6.75</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.194</v>
+        <v>0.148</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.058</v>
+        <v>0.148</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.163</v>
+        <v>0.204</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#87 A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>65</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" t="n">
+        <v>40</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>17</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>13</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>28</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9</v>
+      </c>
+      <c r="V20" t="n">
+        <v>14</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3</v>
+      </c>
+      <c r="X20" t="n">
         <v>2</v>
       </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="Y20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
         <v>5</v>
       </c>
-      <c r="L20" t="n">
+      <c r="AD20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" t="n">
         <v>3</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>111:15</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>80.2</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>8.571</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>9.429</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>#95 D. CALERO BAUTISTA</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>23</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>11</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
         <v>2</v>
       </c>
-      <c r="C21" t="n">
-        <v>147</v>
-      </c>
-      <c r="D21" t="n">
-        <v>32</v>
-      </c>
-      <c r="E21" t="n">
-        <v>76</v>
-      </c>
-      <c r="F21" t="n">
-        <v>15</v>
-      </c>
-      <c r="G21" t="n">
-        <v>61</v>
-      </c>
-      <c r="H21" t="n">
-        <v>38</v>
-      </c>
-      <c r="I21" t="n">
-        <v>66</v>
-      </c>
-      <c r="J21" t="n">
-        <v>27</v>
-      </c>
-      <c r="K21" t="n">
-        <v>68</v>
-      </c>
-      <c r="L21" t="n">
-        <v>35</v>
-      </c>
-      <c r="M21" t="n">
-        <v>21</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>4</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>3</v>
       </c>
-      <c r="P21" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>11</v>
-      </c>
       <c r="R21" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="V21" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="Z21" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.483</v>
+        <v>0.5</v>
       </c>
       <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK21" t="n">
         <v>2</v>
       </c>
-      <c r="AC21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="AL21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM21" t="n">
         <v>0.25</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>64:42</t>
+        </is>
+      </c>
+      <c r="AO21" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AV21" t="n">
         <v>9</v>
       </c>
-      <c r="AL21" t="n">
-        <v>37</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>400:00</t>
-        </is>
-      </c>
-      <c r="AO21" t="n">
-        <v>197.04</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="AS21" t="n">
+      <c r="AW21" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>0.157</v>
       </c>
-      <c r="AT21" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>4.419</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0.132</v>
-      </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>14</v>
       </c>
-      <c r="G22" t="n">
-        <v>64</v>
-      </c>
-      <c r="H22" t="n">
-        <v>24</v>
-      </c>
-      <c r="I22" t="n">
-        <v>43</v>
-      </c>
-      <c r="J22" t="n">
-        <v>25</v>
-      </c>
-      <c r="K22" t="n">
-        <v>61</v>
-      </c>
       <c r="L22" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>5</v>
       </c>
-      <c r="P22" t="n">
-        <v>34</v>
-      </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.448</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.263</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.186</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>400:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>192.92</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.379</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.409</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.735</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.118</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.853</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.068</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.127</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3900,222 +3900,328 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
-      <c r="BA23" t="inlineStr"/>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>352</v>
+      </c>
+      <c r="D23" t="n">
+        <v>87</v>
+      </c>
+      <c r="E23" t="n">
+        <v>209</v>
+      </c>
+      <c r="F23" t="n">
+        <v>39</v>
+      </c>
+      <c r="G23" t="n">
+        <v>156</v>
+      </c>
+      <c r="H23" t="n">
+        <v>61</v>
+      </c>
+      <c r="I23" t="n">
+        <v>117</v>
+      </c>
+      <c r="J23" t="n">
+        <v>75</v>
+      </c>
+      <c r="K23" t="n">
+        <v>146</v>
+      </c>
+      <c r="L23" t="n">
+        <v>95</v>
+      </c>
+      <c r="M23" t="n">
+        <v>44</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9</v>
+      </c>
+      <c r="O23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P23" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>34</v>
+      </c>
+      <c r="R23" t="n">
+        <v>109</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>216</v>
+      </c>
+      <c r="U23" t="n">
+        <v>47</v>
+      </c>
+      <c r="V23" t="n">
+        <v>42</v>
+      </c>
+      <c r="W23" t="n">
+        <v>52</v>
+      </c>
+      <c r="X23" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>146</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>45</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>111</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>1000:00</t>
+        </is>
+      </c>
+      <c r="AO23" t="n">
+        <v>488.48</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>5.069</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>6.111</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>#1 M. ALONSO ARNEDO (Per Game)</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E24" t="n">
+        <v>175</v>
+      </c>
+      <c r="F24" t="n">
+        <v>42</v>
+      </c>
+      <c r="G24" t="n">
+        <v>151</v>
+      </c>
+      <c r="H24" t="n">
+        <v>83</v>
+      </c>
+      <c r="I24" t="n">
+        <v>121</v>
+      </c>
+      <c r="J24" t="n">
+        <v>75</v>
+      </c>
+      <c r="K24" t="n">
+        <v>159</v>
+      </c>
+      <c r="L24" t="n">
+        <v>71</v>
+      </c>
+      <c r="M24" t="n">
+        <v>38</v>
+      </c>
+      <c r="N24" t="n">
+        <v>12</v>
+      </c>
+      <c r="O24" t="n">
+        <v>11</v>
+      </c>
+      <c r="P24" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>35</v>
+      </c>
+      <c r="R24" t="n">
+        <v>117</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>254</v>
+      </c>
+      <c r="U24" t="n">
+        <v>53</v>
+      </c>
+      <c r="V24" t="n">
+        <v>36</v>
+      </c>
+      <c r="W24" t="n">
+        <v>36</v>
+      </c>
+      <c r="X24" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>145</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG24" t="n">
         <v>0.5</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>00:34</t>
+          <t>1000:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>0.5</v>
+        <v>458.24</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>0.439</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>0.486</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>0.805</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>0.949</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>4.127</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>5.076</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.353</v>
+        <v>0.2</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="BA24" t="n">
         <v>0</v>
@@ -4124,209 +4230,103 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>#2 J. MERENCIO MORENO (Per Game)</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" t="n">
-        <v>12</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>8</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>12</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>28:45</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>15.14</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.793</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0.171</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#3 J. VALERO CHICA (Per Game)</t>
+          <t>#1 M. ALONSO ARNEDO (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4335,10 +4335,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -4365,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -4392,60 +4392,60 @@
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>03:48</t>
+          <t>01:48</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>2.44</v>
+        <v>0.6</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.515</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
         <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.26</v>
+        <v>0.136</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.102</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
         <v>0</v>
@@ -4454,731 +4454,731 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#10 P. LOPEZ DOMINGUEZ (Per Game)</t>
+          <t>#2 J. MERENCIO MORENO (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.2</v>
+        <v>0.182</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>30:34</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>6.38</v>
+        <v>12.848</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.278</v>
+        <v>0.286</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.372</v>
+        <v>0.361</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.627</v>
+        <v>0.654</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.157</v>
+        <v>0.093</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>2.833</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.5</v>
+        <v>8.167</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.174</v>
+        <v>0.172</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.104</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#12 A. SAEZ CALABUIG (Per Game)</t>
+          <t>#3 J. VALERO CHICA (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>0.5</v>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
         <v>3</v>
       </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>9</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4</v>
-      </c>
       <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
       <c r="AL28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>03:48</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>10.54</v>
+        <v>2.44</v>
       </c>
       <c r="AP28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="AT28" t="n">
         <v>0.333</v>
       </c>
-      <c r="AQ28" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0.167</v>
-      </c>
       <c r="AU28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.203</v>
+        <v>0.262</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.099</v>
+        <v>0.103</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.184</v>
+        <v>0.121</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#16 C. CAMPILLOS ALONSO (Per Game)</t>
+          <t>#10 P. LOPEZ DOMINGUEZ (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K29" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD29" t="n">
         <v>0.5</v>
       </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>0.5</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>14</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
       <c r="AK29" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="AL29" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.375</v>
+        <v>0.143</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>7.16</v>
+        <v>5.928</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.707</v>
+        <v>0.304</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.117</v>
+        <v>0.506</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.209</v>
+        <v>0.169</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.3</v>
+        <v>0.182</v>
       </c>
       <c r="AU29" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.333</v>
+        <v>4.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.333</v>
+        <v>6</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.164</v>
+        <v>0.141</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="AZ29" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="BA29" t="n">
         <v>0.066</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#17 E. LLACER SIMLAT (Per Game)</t>
+          <t>#12 A. SAEZ CALABUIG (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="C30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E30" t="n">
-        <v>6</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="Q30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>26</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y30" t="n">
         <v>2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.5</v>
       </c>
       <c r="Z30" t="n">
         <v>4</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AC30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG30" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>23:47</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>10.88</v>
+        <v>9.92</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.167</v>
+        <v>0.409</v>
       </c>
       <c r="AQ30" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AS30" t="n">
         <v>0.202</v>
       </c>
-      <c r="AR30" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0.092</v>
-      </c>
       <c r="AT30" t="n">
-        <v>0.111</v>
+        <v>0.121</v>
       </c>
       <c r="AU30" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AV30" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="AW30" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.277</v>
+        <v>0.171</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.078</v>
+        <v>0.079</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.17</v>
+        <v>0.178</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.045</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#22 J. BEDIA FERRER (Per Game)</t>
+          <t>#16 C. CAMPILLOS ALONSO (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="E31" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="J31" t="n">
         <v>1.5</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="L31" t="n">
-        <v>5.5</v>
+        <v>0.25</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R31" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
       <c r="V31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -5187,19 +5187,19 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>0.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -5223,100 +5223,100 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>7.1</v>
+        <v>6.58</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.545</v>
+        <v>0.395</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.53</v>
+        <v>0.443</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.986</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.228</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.182</v>
+        <v>0.158</v>
       </c>
       <c r="AU31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>3.167</v>
       </c>
       <c r="AW31" t="n">
-        <v>14</v>
+        <v>4.167</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.14</v>
+        <v>0.196</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.223</v>
+        <v>0.014</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.076</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.073</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#24 F. GOMEZ CARBONELL (Per Game)</t>
+          <t>#17 E. LLACER SIMLAT (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>9.5</v>
+        <v>7.4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="G32" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -5325,211 +5325,211 @@
         <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AH32" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.444</v>
+        <v>0.333</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>23:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>7.22</v>
+        <v>12.344</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.327</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.707</v>
+        <v>0.338</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.316</v>
+        <v>0.599</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.113</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.077</v>
+        <v>0.102</v>
       </c>
       <c r="AU32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV32" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AW32" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.126</v>
+        <v>0.292</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.018</v>
+        <v>0.045</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.067</v>
+        <v>0.117</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.125</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#55 L. BLASCO NAVARRO (Per Game)</t>
+          <t>#22 J. BEDIA FERRER (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="E33" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M33" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V33" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5553,265 +5553,265 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>4</v>
+        <v>8.592000000000001</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.3</v>
+        <v>0.607</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.3</v>
+        <v>0.626</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.375</v>
+        <v>0.931</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.375</v>
+        <v>0.256</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.667</v>
+        <v>2.545</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.667</v>
+        <v>3</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.134</v>
+        <v>0.15</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.137</v>
+        <v>0.168</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.224</v>
+        <v>0.141</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#87 A. TERRADES DAROQUI (Per Game)</t>
+          <t>#24 F. GOMEZ CARBONELL (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M34" t="n">
         <v>2</v>
       </c>
-      <c r="C34" t="n">
-        <v>16</v>
-      </c>
-      <c r="D34" t="n">
-        <v>4</v>
-      </c>
-      <c r="E34" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>27</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="AU34" t="n">
         <v>3</v>
       </c>
-      <c r="H34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I34" t="n">
-        <v>11</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>18</v>
-      </c>
-      <c r="U34" t="n">
-        <v>3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>27:02</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>1</v>
-      </c>
       <c r="AV34" t="n">
-        <v>6.25</v>
+        <v>8.75</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.25</v>
+        <v>11.75</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.29</v>
+        <v>0.183</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.062</v>
+        <v>0.034</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.144</v>
+        <v>0.05</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#95 D. CALERO BAUTISTA (Per Game)</t>
+          <t>#26 M. ISIDRO PEÑA (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5820,13 +5820,13 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -5835,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5847,19 +5847,19 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
         <v>0</v>
@@ -5886,213 +5886,213 @@
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
         <v>0</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>02:08</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.387</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.147</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.058</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.163</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#33 Ó. GONZÁLEZ JURADO (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L36" t="n">
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>01:48</t>
+        </is>
+      </c>
+      <c r="AO36" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="AP36" t="n">
         <v>1.5</v>
       </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.064</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.031</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>0.515</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="n">
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>0.292</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="AZ36" t="n">
         <v>0</v>
@@ -6104,330 +6104,990 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>TOTAL (Per Game)</t>
+          <t>#55 L. BLASCO NAVARRO (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>73.5</v>
+        <v>5.4</v>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>1.2</v>
       </c>
       <c r="E37" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>44</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
+        <v>6.552</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AW37" t="n">
         <v>7.5</v>
       </c>
-      <c r="G37" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>19</v>
-      </c>
-      <c r="I37" t="n">
-        <v>33</v>
-      </c>
-      <c r="J37" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="K37" t="n">
-        <v>34</v>
-      </c>
-      <c r="L37" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3</v>
-      </c>
-      <c r="P37" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>20</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>104</v>
-      </c>
-      <c r="U37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="V37" t="n">
-        <v>12</v>
-      </c>
-      <c r="W37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="X37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>98.52</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>4.419</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>5.29</v>
-      </c>
       <c r="AX37" t="n">
-        <v>0.2</v>
+        <v>0.148</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.073</v>
+        <v>0.148</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.132</v>
+        <v>0.204</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Rival (Per Game)</t>
+          <t>#87 A. TERRADES DAROQUI (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>13</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L38" t="n">
         <v>2</v>
       </c>
-      <c r="C38" t="n">
-        <v>65</v>
-      </c>
-      <c r="D38" t="n">
-        <v>16</v>
-      </c>
-      <c r="E38" t="n">
-        <v>38</v>
-      </c>
-      <c r="F38" t="n">
-        <v>7</v>
-      </c>
-      <c r="G38" t="n">
-        <v>32</v>
-      </c>
-      <c r="H38" t="n">
-        <v>12</v>
-      </c>
-      <c r="I38" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J38" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K38" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="L38" t="n">
-        <v>17.5</v>
-      </c>
       <c r="M38" t="n">
-        <v>10</v>
+        <v>0.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>17</v>
+        <v>1.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="R38" t="n">
-        <v>27.5</v>
+        <v>2.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="U38" t="n">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="V38" t="n">
-        <v>12</v>
+        <v>2.8</v>
       </c>
       <c r="W38" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="X38" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>15</v>
+        <v>2.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>33.5</v>
+        <v>6</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.448</v>
+        <v>0.433</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="AD38" t="n">
         <v>0.2</v>
       </c>
       <c r="AE38" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>0.333</v>
       </c>
-      <c r="AH38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.263</v>
-      </c>
       <c r="AK38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AL38" t="n">
-        <v>21.5</v>
+        <v>3.4</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.186</v>
+        <v>0.294</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>8.571</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>9.429</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>#95 D. CALERO BAUTISTA (Per Game)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AO39" t="n">
+        <v>8.616</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Equip (Per Game)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL (Per Game)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="D41" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G41" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="J41" t="n">
+        <v>15</v>
+      </c>
+      <c r="K41" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>19</v>
+      </c>
+      <c r="M41" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O41" t="n">
+        <v>10</v>
+      </c>
+      <c r="P41" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="R41" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>216</v>
+      </c>
+      <c r="U41" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="V41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="X41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
           <t>200:00</t>
         </is>
       </c>
-      <c r="AO38" t="n">
-        <v>96.45999999999999</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>4.118</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>4.853</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="BA38" t="n">
+      <c r="AO41" t="n">
+        <v>97.696</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>5.069</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>6.111</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Rival (Per Game)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16</v>
+      </c>
+      <c r="E42" t="n">
+        <v>35</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G42" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>15</v>
+      </c>
+      <c r="K42" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="L42" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>11</v>
+      </c>
+      <c r="P42" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R42" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>254</v>
+      </c>
+      <c r="U42" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>200:00</t>
+        </is>
+      </c>
+      <c r="AO42" t="n">
+        <v>91.648</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>4.127</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>5.076</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="BA42" t="n">
         <v>0</v>
       </c>
     </row>
